--- a/public/post/drafts/season-prediction/men_model-exhaustive-tests-predicted_rmse.xlsx
+++ b/public/post/drafts/season-prediction/men_model-exhaustive-tests-predicted_rmse.xlsx
@@ -50,10 +50,10 @@
     <t xml:space="preserve">Weighted</t>
   </si>
   <si>
+    <t xml:space="preserve">Random Forest</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tobit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Forest</t>
   </si>
   <si>
     <t xml:space="preserve">Quantile</t>
@@ -535,25 +535,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>0.137612469588276</v>
+        <v>0.138914060105858</v>
       </c>
       <c r="C6" t="n">
-        <v>0.143587105029685</v>
+        <v>0.140016870895762</v>
       </c>
       <c r="D6" t="n">
-        <v>0.208742864388849</v>
+        <v>0.195684792174801</v>
       </c>
       <c r="E6" t="n">
-        <v>0.142538624693651</v>
+        <v>0.139769866986141</v>
       </c>
       <c r="F6" t="n">
-        <v>0.117180937951465</v>
+        <v>0.116876138360359</v>
       </c>
       <c r="G6" t="n">
-        <v>0.144854295902901</v>
+        <v>0.160131872787236</v>
       </c>
       <c r="H6" t="n">
-        <v>0.149086049592471</v>
+        <v>0.148565600218359</v>
       </c>
     </row>
     <row r="7">
@@ -561,25 +561,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>0.139106741440117</v>
+        <v>0.137612469588276</v>
       </c>
       <c r="C7" t="n">
-        <v>0.141986365481611</v>
+        <v>0.143587105029685</v>
       </c>
       <c r="D7" t="n">
-        <v>0.196214469492203</v>
+        <v>0.208742864388849</v>
       </c>
       <c r="E7" t="n">
-        <v>0.141697814443991</v>
+        <v>0.142538624693651</v>
       </c>
       <c r="F7" t="n">
-        <v>0.115305576566594</v>
+        <v>0.117180937951465</v>
       </c>
       <c r="G7" t="n">
-        <v>0.163658835385999</v>
+        <v>0.144854295902901</v>
       </c>
       <c r="H7" t="n">
-        <v>0.149661633801753</v>
+        <v>0.149086049592471</v>
       </c>
     </row>
     <row r="8">
